--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -519,6 +519,9 @@
       <c r="C11" t="str">
         <v>742_袋鼠爪绿_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -577,7 +580,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015302020555550</v>
+        <v>015302020555555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -523,9 +523,177 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>517_鼠尾粉色_veronica pink_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>771_美洲茶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="C14" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>325_小盼草_Northern Sea Oats_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2</v>
+      </c>
+      <c r="C17" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="C20" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F21" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>769_菟葵绿铃铛_undefined_undefined_undefinedundefined</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>85_摩洛哥_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>83_布拉格_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>3</v>
+      </c>
+      <c r="C28" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>421_松虫草黑色_scabiosa black_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -580,7 +748,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015302020555555</v>
+        <v>015302020555555101066151010101420555555101050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -690,6 +690,9 @@
       <c r="C31" t="str">
         <v>421_松虫草黑色_scabiosa black_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -748,7 +751,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015302020555555101066151010101420555555101050</v>
+        <v>015302020555555101066151010101420555555101055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -690,9 +690,6 @@
       <c r="C31" t="str">
         <v>421_松虫草黑色_scabiosa black_undefined_1bunch</v>
       </c>
-      <c r="F31" t="str">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -751,7 +748,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015302020555555101066151010101420555555101055</v>
+        <v>015302020555555101066151010101420555555101050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -688,12 +688,23 @@
     </row>
     <row r="31">
       <c r="C31" t="str">
-        <v>421_松虫草黑色_scabiosa black_undefined_1bunch</v>
+        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
+      </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>514_松虫草紫_scabiosa purple_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -748,7 +759,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015302020555555101066151010101420555555101050</v>
+        <v>0153020205555551010661510101014205555551010555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -761,6 +761,9 @@
       <c r="G2" t="str">
         <v>0153020205555551010661510101014205555551010555</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,39 +443,41 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>316_尤加利叶大叶_Eucalyptus Cinerea_undefined_1bunch</v>
+        <v>742_袋鼠爪绿_undefined_undefined_1bunch</v>
       </c>
       <c r="F2" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="C3" t="str">
-        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="C3" t="str" xml:space="preserve">
+        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
       </c>
       <c r="F3" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="C4" t="str">
-        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="C4" t="str" xml:space="preserve">
+        <v xml:space="preserve">740_袋鼠爪橙_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
       </c>
       <c r="F4" t="str">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="str">
-        <v>109_绣球国产绿_Hydrangea Colombia Green (local)_Hydrangea L._1stem</v>
+        <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
       </c>
       <c r="F5" t="str">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" t="str">
-        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+        <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
       </c>
       <c r="F6" t="str">
         <v>5</v>
@@ -483,15 +485,16 @@
     </row>
     <row r="7">
       <c r="C7" t="str">
-        <v>571_大飞燕浅紫_undefined_undefined_1bunch</v>
+        <v>324_小手球单瓣_Spiraea flower_undefined_1bunch</v>
       </c>
       <c r="F7" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" t="str">
-        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="C8" t="str" xml:space="preserve">
+        <v xml:space="preserve">349_千层金绿_Melaleuca bracteata
+（dyed orange）_Melaleuca bracteata F.Muell._1bunch</v>
       </c>
       <c r="F8" t="str">
         <v>5</v>
@@ -499,17 +502,16 @@
     </row>
     <row r="9" xml:space="preserve">
       <c r="C9" t="str" xml:space="preserve">
-        <v xml:space="preserve">740_袋鼠爪橙_Kangaroo Paw
-red /green /orange / yellow_undefined_1bunch</v>
+        <v xml:space="preserve">350_千层金红_Melaleuca bracteata
+（dyed red）_Melaleuca bracteata F.Muell._1bunch</v>
       </c>
       <c r="F9" t="str">
         <v>5</v>
       </c>
     </row>
-    <row r="10" xml:space="preserve">
-      <c r="C10" t="str" xml:space="preserve">
-        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
-red /green /orange / yellow_undefined_1bunch</v>
+    <row r="10">
+      <c r="C10" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
       </c>
       <c r="F10" t="str">
         <v>5</v>
@@ -517,7 +519,7 @@
     </row>
     <row r="11">
       <c r="C11" t="str">
-        <v>742_袋鼠爪绿_undefined_undefined_1bunch</v>
+        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
       </c>
       <c r="F11" t="str">
         <v>5</v>
@@ -525,35 +527,34 @@
     </row>
     <row r="12">
       <c r="C12" t="str">
-        <v>517_鼠尾粉色_veronica pink_undefined_1bunch</v>
+        <v>496_大飞燕深蓝色_delphinium dark blue_undefined_1bunch</v>
       </c>
       <c r="F12" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" t="str">
-        <v>771_美洲茶_undefined_undefined_1bunch</v>
+        <v>402_大飞燕深紫色_delphinium purple_undefined_1bunch</v>
       </c>
       <c r="F13" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="C14" t="str" xml:space="preserve">
-        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
-white_Trachymene Coerulea_1bunch</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>571_大飞燕浅紫_undefined_undefined_1bunch</v>
       </c>
       <c r="F14" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" t="str">
-        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
+        <v>495_大飞燕深粉色_delphinium pink_undefined_1bunch</v>
       </c>
       <c r="F15" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -565,11 +566,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>2</v>
-      </c>
       <c r="C17" t="str">
-        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+        <v>356_绿枫叶山货_maple leaf small_undefined_1bunch</v>
       </c>
       <c r="F17" t="str">
         <v>10</v>
@@ -577,56 +575,58 @@
     </row>
     <row r="18">
       <c r="C18" t="str">
-        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+        <v>329_柔丝_undefined_undefined_1bunch</v>
       </c>
       <c r="F18" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="C19" t="str">
-        <v>602_康乃馨白_white_undefined_20stems</v>
+        <v>329_柔丝_undefined_undefined_1bunch</v>
       </c>
       <c r="F19" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
-      <c r="C20" t="str" xml:space="preserve">
-        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
-white_Trachymene Coerulea_1bunch</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
       </c>
       <c r="F20" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="str">
-        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+        <v>110_绣球浅蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
       </c>
       <c r="F21" t="str">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" t="str">
-        <v>769_菟葵绿铃铛_undefined_undefined_undefinedundefined</v>
+        <v>432_小刺秦/情人果_small Eryngium_undefined_1bunch</v>
       </c>
       <c r="F22" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="str">
+        <v>2</v>
+      </c>
       <c r="C23" t="str">
-        <v>85_摩洛哥_undefined_Gerbera L._10stems</v>
+        <v>217_琉璃翠_Dynamic_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F23" t="str">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="C24" t="str">
-        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+        <v>280_杏仁果汁_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F24" t="str">
         <v>5</v>
@@ -634,77 +634,60 @@
     </row>
     <row r="25">
       <c r="C25" t="str">
-        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F25" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" t="str">
-        <v>83_布拉格_undefined_Gerbera L._10stems</v>
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
       </c>
       <c r="F26" t="str">
         <v>5</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v/>
-      </c>
       <c r="C27" t="str">
-        <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F27" t="str">
         <v>5</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>3</v>
-      </c>
       <c r="C28" t="str">
-        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F28" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="C29" t="str">
-        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+        <v>229_黄蝴蝶_Yellow Butterfly_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F29" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" t="str">
-        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F30" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="str">
-        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
-      </c>
-      <c r="F31" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="str">
-        <v>514_松虫草紫_scabiosa purple_undefined_1bunch</v>
-      </c>
-      <c r="F32" t="str">
-        <v>5</v>
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -759,10 +742,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0153020205555551010661510101014205555551010555</v>
-      </c>
-      <c r="H2" t="str">
-        <v>CNY</v>
+        <v>010555510555553331510552010108510555630</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -684,6 +684,9 @@
       <c r="C31" t="str">
         <v>300_白星_White Gypso_ gypsophila_1kg</v>
       </c>
+      <c r="F31" t="str">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -742,7 +745,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010555510555553331510552010108510555630</v>
+        <v>010555510555553331510552010108510555636</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -688,9 +688,503 @@
         <v>6</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>3</v>
+      </c>
+      <c r="C32" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>255_九星蓝狐_Ocean Song spray_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
+      </c>
+      <c r="F40" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>624_多丁白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>4</v>
+      </c>
+      <c r="C42" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>5</v>
+      </c>
+      <c r="C49" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F51" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F52" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F53" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>611_康乃馨奶油白_cream white_undefined_20stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>6</v>
+      </c>
+      <c r="C57" t="str">
+        <v>316_尤加利叶大叶_Eucalyptus Cinerea_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>436_木百合_leucadendron _undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>423_鼠尾紫色_veronica purple_undefined_1bunch</v>
+      </c>
+      <c r="F61" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>424_鼠尾白色_veronica white_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>517_鼠尾粉色_veronica pink_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>558_油画小菊_Helenium_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" xml:space="preserve">
+      <c r="C65" t="str" xml:space="preserve">
+        <v xml:space="preserve">416_翠珠紫_Didiscus caeruleus
+blue_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" xml:space="preserve">
+      <c r="C66" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68" t="str">
+        <v>7</v>
+      </c>
+      <c r="C68" t="str" xml:space="preserve">
+        <v xml:space="preserve">417_黑种草蓝色_nigella damascena 
+blue_undefined_1bunch</v>
+      </c>
+      <c r="F68" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
+      <c r="C69" t="str" xml:space="preserve">
+        <v xml:space="preserve">511_黑种草白色_nigella damascena 
+white_undefined_1bunch</v>
+      </c>
+      <c r="F69" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>773_格桑花白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F70" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>772_格桑花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F71" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F72" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F73" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F74" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" t="str">
+        <v>770_弯葱_undefined_undefined_10stems</v>
+      </c>
+      <c r="F75" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" t="str">
+        <v>707_永生吊米白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F76" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>8</v>
+      </c>
+      <c r="C77" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F77" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="str">
+        <v>84_堪培拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F78" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F79" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" t="str">
+        <v>764_芍药莎拉多头_undefined_undefined_10stems</v>
+      </c>
+      <c r="F80" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="str">
+        <v>738_鸢尾花蓝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F81" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F82" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F83" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" t="str">
+        <v>748_紫罗兰浅粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F84" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>9</v>
+      </c>
+      <c r="C85" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F85" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F86" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" t="str">
+        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
+      </c>
+      <c r="F87" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F88" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F89" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L90"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -745,7 +1239,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010555510555553331510552010108510555636</v>
+        <v>010555510555553331510552010108510555636581025565458829511667105310201520105205551015101455555155101510101545355510555100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -1181,6 +1181,9 @@
       <c r="A90" t="str">
         <v>10</v>
       </c>
+      <c r="C90" t="str">
+        <v>570_水蜡烛_undefined_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -1184,6 +1184,9 @@
       <c r="C90" t="str">
         <v>570_水蜡烛_undefined_undefined_1bunch</v>
       </c>
+      <c r="F90" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1242,7 +1245,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010555510555553331510552010108510555636581025565458829511667105310201520105205551015101455555155101510101545355510555100</v>
+        <v>0105555105555533315105520101085105556365810255654588295116671053102015201052055510151014555551551015101015453555105551010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-10.xlsx
@@ -1247,6 +1247,9 @@
       <c r="G2" t="str">
         <v>0105555105555533315105520101085105556365810255654588295116671053102015201052055510151014555551551015101015453555105551010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
